--- a/source.xlsx
+++ b/source.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suresh/Desktop/App/ExcelMapper/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEDB5C2-CE2B-3F4B-8261-B03BBD090251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="480" windowWidth="28800" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Gen. Journal Line"/>
+    <sheet name="Gen. Journal Line" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="84">
   <si>
     <t>Journal Template Name</t>
   </si>
@@ -260,13 +266,18 @@
   </si>
   <si>
     <t>11841</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>20000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -309,90 +320,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AU3" displayName="Table5" name="Table5" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:AU3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A1:AU3" totalsRowShown="0">
+  <autoFilter ref="A1:AU3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="47">
-    <tableColumn name="Journal Template Name" id="1"/>
-    <tableColumn name="Journal Batch Name" id="2"/>
-    <tableColumn name="Line No." id="3"/>
-    <tableColumn name="Account Type" id="4"/>
-    <tableColumn name="Account No." id="5"/>
-    <tableColumn name="Posting Date" id="6"/>
-    <tableColumn name="Document Type" id="7"/>
-    <tableColumn name="Document No." id="8"/>
-    <tableColumn name="Bal. Account No." id="9"/>
-    <tableColumn name="Debit Amount" id="10"/>
-    <tableColumn name="Credit Amount" id="11"/>
-    <tableColumn name="Shortcut Dimension 1 Code" id="12"/>
-    <tableColumn name="Bal. Account Type" id="13"/>
-    <tableColumn name="Location Code" id="14"/>
-    <tableColumn name="Academic Year" id="15"/>
-    <tableColumn name="Fee Code" id="16"/>
-    <tableColumn name="Program Code" id="17"/>
-    <tableColumn name="Admitted Year" id="18"/>
-    <tableColumn name="Voucher Type" id="19"/>
-    <tableColumn name="UTR No." id="20"/>
-    <tableColumn name="School Code" id="21"/>
-    <tableColumn name="Admission Type" id="22"/>
-    <tableColumn name="PG Type" id="23"/>
-    <tableColumn name="Registration No." id="24"/>
-    <tableColumn name="Application No." id="25"/>
-    <tableColumn name="Specialization Code" id="26"/>
-    <tableColumn name="Batch Year" id="27"/>
-    <tableColumn name="Academic Term" id="28"/>
-    <tableColumn name="Student No." id="29"/>
-    <tableColumn name="Occupancy" id="30"/>
-    <tableColumn name="Transport Slab" id="31"/>
-    <tableColumn name="Voucher Reference Date" id="32"/>
-    <tableColumn name="Voucher Reference No." id="33"/>
-    <tableColumn name="Transportation Slab Code" id="34"/>
-    <tableColumn name="Transportation Admitted Year" id="35"/>
-    <tableColumn name="Transportation Slab Name" id="36"/>
-    <tableColumn name="Hostel Block Code" id="37"/>
-    <tableColumn name="Hostel Admitted Year" id="38"/>
-    <tableColumn name="Academic Quota Code" id="39"/>
-    <tableColumn name="Bus Route Code" id="40"/>
-    <tableColumn name="kilometers" id="41"/>
-    <tableColumn name="Student Name" id="42"/>
-    <tableColumn name="Narration" id="43"/>
-    <tableColumn name="Pickup Point Code" id="44"/>
-    <tableColumn name="Route Code" id="45"/>
-    <tableColumn name="Accomodation Code" id="46"/>
-    <tableColumn name="Year" id="47"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Journal Template Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Journal Batch Name"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Line No."/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Account Type"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Account No."/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Posting Date"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Document Type"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Document No."/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Bal. Account No."/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Debit Amount"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Credit Amount"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Shortcut Dimension 1 Code"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Bal. Account Type"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Location Code"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Academic Year"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Fee Code"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Program Code"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Admitted Year"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Voucher Type"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="UTR No."/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="School Code"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Admission Type"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="PG Type"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Registration No."/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Application No."/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Specialization Code"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Batch Year"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Academic Term"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Student No."/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Occupancy"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Transport Slab"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Voucher Reference Date"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Voucher Reference No."/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Transportation Slab Code"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Transportation Admitted Year"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Transportation Slab Name"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Hostel Block Code"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Hostel Admitted Year"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Academic Quota Code"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Bus Route Code"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="kilometers"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Student Name"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Narration"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Pickup Point Code"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Route Code"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Accomodation Code"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Year"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -401,10 +410,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -442,71 +451,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -534,7 +543,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -557,11 +566,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -570,13 +579,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -586,7 +595,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -595,7 +604,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -604,7 +613,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -612,10 +621,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -680,63 +689,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AU3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="4" width="25.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="28" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="29" customWidth="1"/>
+    <col min="36" max="40" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="42" max="47" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row r="1" spans="1:47" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -879,7 +855,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row r="2" spans="1:47" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
@@ -908,7 +884,7 @@
         <v>55</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>57</v>
@@ -994,7 +970,7 @@
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row r="3" spans="1:47" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -1023,7 +999,7 @@
         <v>55</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>77</v>
